--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="355">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -623,15 +623,6 @@
     <t>A code or name that describes this diagnostic report.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="57698-3"/&gt;
-    &lt;display value="Lipid panel with direct LDL - Serum or Plasma"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
@@ -865,9 +856,6 @@
   <si>
     <t>Data
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Observation)
@@ -3160,7 +3148,7 @@
         <v>80</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>80</v>
@@ -3178,10 +3166,10 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3214,28 +3202,28 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3254,17 +3242,17 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3313,7 +3301,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3328,28 +3316,28 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3368,19 +3356,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3429,7 +3417,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3444,28 +3432,28 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3484,19 +3472,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3545,7 +3533,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3560,28 +3548,28 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3600,19 +3588,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3661,7 +3649,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3679,25 +3667,25 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3716,19 +3704,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3777,7 +3765,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3792,28 +3780,28 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3832,19 +3820,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="O21" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3893,7 +3881,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3908,24 +3896,24 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3948,19 +3936,19 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4009,7 +3997,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4027,10 +4015,10 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4038,18 +4026,18 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -4064,19 +4052,19 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4113,17 +4101,17 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4141,10 +4129,10 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4152,20 +4140,20 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="D24" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4180,19 +4168,19 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4241,7 +4229,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4259,10 +4247,10 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -4270,20 +4258,20 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -4298,19 +4286,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4359,7 +4347,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4377,10 +4365,10 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4388,20 +4376,20 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4416,19 +4404,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4477,7 +4465,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4495,10 +4483,10 @@
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -4506,20 +4494,20 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -4534,19 +4522,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4595,7 +4583,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4613,10 +4601,10 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4624,16 +4612,16 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4652,19 +4640,19 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4713,7 +4701,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4731,10 +4719,10 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4742,16 +4730,16 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="D29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4770,19 +4758,19 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4831,7 +4819,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4849,10 +4837,10 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4860,16 +4848,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="D30" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4888,19 +4876,19 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -4949,7 +4937,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4967,10 +4955,10 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4978,10 +4966,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5004,16 +4992,16 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5063,7 +5051,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5084,7 +5072,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5092,14 +5080,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5118,17 +5106,17 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5177,7 +5165,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5195,10 +5183,10 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5206,10 +5194,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5232,13 +5220,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5289,7 +5277,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5310,7 +5298,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5318,10 +5306,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5350,7 +5338,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -5403,7 +5391,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5424,7 +5412,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5432,14 +5420,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5461,10 +5449,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -5519,7 +5507,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5548,10 +5536,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5574,19 +5562,19 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5635,7 +5623,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5656,7 +5644,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5664,10 +5652,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5690,13 +5678,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5747,7 +5735,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>90</v>
@@ -5768,7 +5756,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5776,14 +5764,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5802,17 +5790,17 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5861,7 +5849,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5879,10 +5867,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -5890,10 +5878,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5919,10 +5907,10 @@
         <v>180</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5952,10 +5940,10 @@
         <v>184</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -5973,7 +5961,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5991,10 +5979,10 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6002,10 +5990,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6028,19 +6016,19 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6089,7 +6077,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6107,10 +6095,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -517,7 +517,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -598,7 +598,7 @@
     <t>Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -635,7 +635,7 @@
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -657,7 +657,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -689,7 +689,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -791,7 +791,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -841,7 +841,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -867,7 +867,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -965,7 +965,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1070,7 +1070,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1472,7 +1472,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.3671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.24609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1487,7 +1487,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="41.5390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.90625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -4147,7 +4147,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>278</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>281</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>284</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>287</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>289</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>292</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>295</v>
       </c>
@@ -6115,12 +6115,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN40">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$39</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="353">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -930,16 +930,6 @@
   </si>
   <si>
     <t>trigly-cholesterol</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:cholesterol-ratio</t>
-  </si>
-  <si>
-    <t>cholesterol-ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-observation-cholesterol-ratio)
-</t>
   </si>
   <si>
     <t>DiagnosticReport.result:cholesterol-aspect</t>
@@ -1459,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.6171875" customWidth="true" bestFit="true"/>
@@ -4855,28 +4845,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
@@ -4885,20 +4873,18 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4946,7 +4932,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4964,10 +4950,10 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4975,14 +4961,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4998,21 +4984,21 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5060,7 +5046,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5078,10 +5064,10 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5089,21 +5075,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5112,21 +5098,19 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5174,28 +5158,28 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5203,21 +5187,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5229,15 +5213,17 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>312</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5286,19 +5272,19 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5307,7 +5293,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5322,7 +5308,7 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>135</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5335,24 +5321,26 @@
         <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>137</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5400,7 +5388,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5421,7 +5409,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>316</v>
+        <v>133</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5429,45 +5417,45 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>139</v>
+        <v>325</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>145</v>
+        <v>326</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5516,19 +5504,19 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5537,7 +5525,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>133</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5545,10 +5533,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5556,7 +5544,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -5568,23 +5556,19 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5632,10 +5616,10 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -5653,7 +5637,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5661,18 +5645,18 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
@@ -5684,19 +5668,21 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5744,10 +5730,10 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>90</v>
@@ -5762,10 +5748,10 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5773,21 +5759,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -5799,18 +5785,16 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5834,13 +5818,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -5858,13 +5842,13 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
@@ -5876,10 +5860,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -5887,10 +5871,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5913,16 +5897,20 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>180</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -5946,31 +5934,31 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5988,133 +5976,17 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN40" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN40">
+  <autoFilter ref="A1:AN39">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6124,7 +5996,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI39">
+  <conditionalFormatting sqref="A2:AI38">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
